--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20261013_233719.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20261013_233719.xlsx
@@ -2492,7 +2492,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20261013_233719.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20261013_233719.xlsx
@@ -2492,7 +2492,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
